--- a/docs/sample-output/09-tiny-home-community/estimate.xlsx
+++ b/docs/sample-output/09-tiny-home-community/estimate.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="337">
   <si>
     <t>FINISHES SOLUTIONS</t>
   </si>
   <si>
-    <t>Total Project Cost — Summary   ·   Cedar Pines tiny home community · Total $3,385,834</t>
+    <t>Total Project Cost — Summary   ·   Cedar Pines tiny home community · Total $3,314,793</t>
   </si>
   <si>
     <t>COST SUMMARY</t>
@@ -90,7 +90,7 @@
     <t>Research data version</t>
   </si>
   <si>
-    <t>2026.7c60a42879</t>
+    <t>2026.0c737c8255</t>
   </si>
   <si>
     <t>Engine</t>
@@ -99,10 +99,10 @@
     <t>budget-engine-2.0.0</t>
   </si>
   <si>
-    <t>All defaults come from the research data shipped with the app (2026.7c60a42879), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
-  </si>
-  <si>
-    <t>Cost by Component   ·   Cedar Pines tiny home community · Total $3,385,834</t>
+    <t>All defaults come from the research data shipped with the app (2026.0c737c8255), escalated to the construction midpoint and adjusted to the project location. Values marked "Derived estimate — verify" have no direct published source.</t>
+  </si>
+  <si>
+    <t>Cost by Component   ·   Cedar Pines tiny home community · Total $3,314,793</t>
   </si>
   <si>
     <t>Component</t>
@@ -147,7 +147,7 @@
     <t>within ($21,771–$141,514)</t>
   </si>
   <si>
-    <t>Cost by Phase   ·   Cedar Pines tiny home community · Total $3,385,834</t>
+    <t>Cost by Phase   ·   Cedar Pines tiny home community · Total $3,314,793</t>
   </si>
   <si>
     <t>Phase</t>
@@ -189,7 +189,7 @@
     <t>4.9%</t>
   </si>
   <si>
-    <t>Line-Item Detail   ·   Cedar Pines tiny home community · Total $3,385,834</t>
+    <t>Line-Item Detail   ·   Cedar Pines tiny home community · Total $3,314,793</t>
   </si>
   <si>
     <t>Group</t>
@@ -435,7 +435,7 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Draw Schedules   ·   Cedar Pines tiny home community · Total $3,385,834</t>
+    <t>Draw Schedules   ·   Cedar Pines tiny home community · Total $3,314,793</t>
   </si>
   <si>
     <t>PHASE 1 — MONTHLY DRAWS</t>
@@ -486,7 +486,7 @@
     <t>2028-03</t>
   </si>
   <si>
-    <t>Sources &amp; Assumptions   ·   Cedar Pines tiny home community · Total $3,385,834</t>
+    <t>Sources &amp; Assumptions   ·   Cedar Pines tiny home community · Total $3,314,793</t>
   </si>
   <si>
     <t>ASSUMPTIONS</t>
@@ -522,7 +522,7 @@
     <t>LTC 60%, rate 7.00%, fee 1.00%</t>
   </si>
   <si>
-    <t>SOURCES (42)</t>
+    <t>SOURCES (43)</t>
   </si>
   <si>
     <t>Ref</t>
@@ -916,6 +916,21 @@
   </si>
   <si>
     <t>150000 USD/project (2025)</t>
+  </si>
+  <si>
+    <t>residential/single-family.json#e10</t>
+  </si>
+  <si>
+    <t>Cost of Constructing a Home-2024 (Special Study for Housing Economics)</t>
+  </si>
+  <si>
+    <t>National Association of Home Builders (Eric Lynch)</t>
+  </si>
+  <si>
+    <t>26747 USD/unit (2024)</t>
+  </si>
+  <si>
+    <t>https://nahb.org/-/media/AB4EFC742624475A97A0A62189986FF8.ashx</t>
   </si>
   <si>
     <t>specialty-residential/rv-park-resort.json#e17</t>
@@ -1601,7 +1616,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="5">
-        <v>284933.13999999996</v>
+        <v>284933.14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1609,7 +1624,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="5">
-        <v>541306.88</v>
+        <v>478518.56</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1617,7 +1632,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="5">
-        <v>113550.05</v>
+        <v>110912.94</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -1625,7 +1640,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="5">
-        <v>77732.67</v>
+        <v>75256.24</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -1633,7 +1648,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="5">
-        <v>41137.83</v>
+        <v>37998.42</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -1641,7 +1656,7 @@
         <v>12</v>
       </c>
       <c r="B14" s="7">
-        <v>1058660.57</v>
+        <v>987619.3</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -1657,7 +1672,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="7">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -1696,7 +1711,7 @@
         <v>22</v>
       </c>
       <c r="B21" s="5">
-        <v>1015750.167</v>
+        <v>994437.786</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1824,16 +1839,16 @@
         <v>1971373.32</v>
       </c>
       <c r="E5" s="13">
-        <v>1058660.57</v>
+        <v>987619.3</v>
       </c>
       <c r="F5" s="13">
         <v>355800</v>
       </c>
       <c r="G5" s="13">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
       <c r="H5" s="13">
-        <v>84645.84725</v>
+        <v>82869.8155</v>
       </c>
       <c r="I5" s="14"/>
       <c r="J5" s="12" t="s">
@@ -1850,13 +1865,13 @@
         <v>1971373.32</v>
       </c>
       <c r="E6" s="16">
-        <v>1058660.57</v>
+        <v>987619.3</v>
       </c>
       <c r="F6" s="16">
         <v>355800</v>
       </c>
       <c r="G6" s="16">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
       <c r="H6" s="15"/>
       <c r="I6" s="15"/>
@@ -1972,19 +1987,19 @@
         <v>1971373.32</v>
       </c>
       <c r="G5" s="13">
-        <v>1058660.57</v>
+        <v>987619.3</v>
       </c>
       <c r="H5" s="13">
         <v>355800</v>
       </c>
       <c r="I5" s="13">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
       <c r="J5" s="13">
-        <v>2031500.33</v>
+        <v>1988875.57</v>
       </c>
       <c r="K5" s="13">
-        <v>57417.67</v>
+        <v>55367.48</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1999,13 +2014,13 @@
         <v>1971373.32</v>
       </c>
       <c r="G6" s="16">
-        <v>1058660.57</v>
+        <v>987619.3</v>
       </c>
       <c r="H6" s="16">
         <v>355800</v>
       </c>
       <c r="I6" s="16">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -2982,10 +2997,10 @@
         <v>123</v>
       </c>
       <c r="H34" s="18">
-        <v>4838.18</v>
+        <v>3407.22</v>
       </c>
       <c r="I34" s="13">
-        <v>116116.32</v>
+        <v>81773.28</v>
       </c>
       <c r="J34" s="12" t="s">
         <v>69</v>
@@ -3014,10 +3029,10 @@
         <v>123</v>
       </c>
       <c r="H35" s="18">
-        <v>4592.44</v>
+        <v>3407.22</v>
       </c>
       <c r="I35" s="13">
-        <v>110218.56</v>
+        <v>81773.28</v>
       </c>
       <c r="J35" s="12" t="s">
         <v>69</v>
@@ -3047,7 +3062,7 @@
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="13">
-        <v>41137.83</v>
+        <v>37998.42</v>
       </c>
       <c r="J36" s="12" t="s">
         <v>69</v>
@@ -3193,7 +3208,7 @@
       </c>
       <c r="H41" s="14"/>
       <c r="I41" s="13">
-        <v>113550.05</v>
+        <v>110912.94</v>
       </c>
       <c r="J41" s="12" t="s">
         <v>69</v>
@@ -3221,7 +3236,7 @@
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="13">
-        <v>57417.67</v>
+        <v>55367.48</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>69</v>
@@ -3249,7 +3264,7 @@
       </c>
       <c r="H43" s="14"/>
       <c r="I43" s="13">
-        <v>20315</v>
+        <v>19888.76</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>69</v>
@@ -3269,7 +3284,7 @@
       <c r="G44" s="15"/>
       <c r="H44" s="15"/>
       <c r="I44" s="16">
-        <v>3385833.89</v>
+        <v>3314792.62</v>
       </c>
       <c r="J44" s="15"/>
     </row>
@@ -3368,13 +3383,13 @@
         <v>0</v>
       </c>
       <c r="C6" s="13">
-        <v>713703.05</v>
+        <v>650914.73</v>
       </c>
       <c r="D6" s="13">
         <v>355800</v>
       </c>
       <c r="E6" s="13">
-        <v>1089818.05</v>
+        <v>1026603.49</v>
       </c>
       <c r="F6" s="13">
         <v>0</v>
@@ -3394,13 +3409,13 @@
         <v>33586.43</v>
       </c>
       <c r="C7" s="13">
-        <v>22268.73</v>
+        <v>21787.35</v>
       </c>
       <c r="D7" s="13">
         <v>0</v>
       </c>
       <c r="E7" s="13">
-        <v>55855.16</v>
+        <v>55373.78</v>
       </c>
       <c r="F7" s="13">
         <v>0</v>
@@ -3420,13 +3435,13 @@
         <v>98470.54</v>
       </c>
       <c r="C8" s="13">
-        <v>22268.73</v>
+        <v>21787.35</v>
       </c>
       <c r="D8" s="13">
         <v>0</v>
       </c>
       <c r="E8" s="13">
-        <v>120739.27</v>
+        <v>120257.89</v>
       </c>
       <c r="F8" s="13">
         <v>0</v>
@@ -3446,22 +3461,22 @@
         <v>156643.97</v>
       </c>
       <c r="C9" s="13">
-        <v>22268.73</v>
+        <v>21787.37</v>
       </c>
       <c r="D9" s="13">
         <v>0</v>
       </c>
       <c r="E9" s="13">
-        <v>87921.08</v>
+        <v>123681.89</v>
       </c>
       <c r="F9" s="13">
-        <v>90991.62</v>
+        <v>54749.45</v>
       </c>
       <c r="G9" s="13">
         <v>0</v>
       </c>
       <c r="H9" s="13">
-        <v>90991.62</v>
+        <v>54749.45</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3472,7 +3487,7 @@
         <v>204142.4</v>
       </c>
       <c r="C10" s="13">
-        <v>22268.73</v>
+        <v>21787.35</v>
       </c>
       <c r="D10" s="13">
         <v>0</v>
@@ -3481,13 +3496,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="13">
-        <v>226411.13</v>
+        <v>225929.75</v>
       </c>
       <c r="G10" s="13">
-        <v>530.78</v>
+        <v>319.37</v>
       </c>
       <c r="H10" s="13">
-        <v>317933.53</v>
+        <v>280998.57</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3498,7 +3513,7 @@
         <v>237728.84</v>
       </c>
       <c r="C11" s="13">
-        <v>22268.78</v>
+        <v>21787.4</v>
       </c>
       <c r="D11" s="13">
         <v>0</v>
@@ -3507,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="13">
-        <v>259997.62</v>
+        <v>259516.24</v>
       </c>
       <c r="G11" s="13">
-        <v>1854.61</v>
+        <v>1639.16</v>
       </c>
       <c r="H11" s="13">
-        <v>579785.76</v>
+        <v>542153.97</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3524,7 +3539,7 @@
         <v>255114.47</v>
       </c>
       <c r="C12" s="13">
-        <v>22268.69</v>
+        <v>21787.31</v>
       </c>
       <c r="D12" s="13">
         <v>0</v>
@@ -3533,13 +3548,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="13">
-        <v>277383.16</v>
+        <v>276901.78</v>
       </c>
       <c r="G12" s="13">
-        <v>3382.08</v>
+        <v>3162.56</v>
       </c>
       <c r="H12" s="13">
-        <v>860551</v>
+        <v>822218.31</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3550,7 +3565,7 @@
         <v>255114.47</v>
       </c>
       <c r="C13" s="13">
-        <v>22268.78</v>
+        <v>21787.4</v>
       </c>
       <c r="D13" s="13">
         <v>0</v>
@@ -3559,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="13">
-        <v>277383.25</v>
+        <v>276901.87</v>
       </c>
       <c r="G13" s="13">
-        <v>5019.88</v>
+        <v>4796.27</v>
       </c>
       <c r="H13" s="13">
-        <v>1142954.13</v>
+        <v>1103916.45</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3576,7 +3591,7 @@
         <v>237728.84</v>
       </c>
       <c r="C14" s="13">
-        <v>22268.69</v>
+        <v>21787.31</v>
       </c>
       <c r="D14" s="13">
         <v>0</v>
@@ -3585,13 +3600,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="13">
-        <v>259997.53</v>
+        <v>259516.15</v>
       </c>
       <c r="G14" s="13">
-        <v>6667.23</v>
+        <v>6439.51</v>
       </c>
       <c r="H14" s="13">
-        <v>1409618.89</v>
+        <v>1369872.11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3602,7 +3617,7 @@
         <v>204142.4</v>
       </c>
       <c r="C15" s="13">
-        <v>22268.78</v>
+        <v>21787.4</v>
       </c>
       <c r="D15" s="13">
         <v>0</v>
@@ -3611,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="F15" s="13">
-        <v>226411.18</v>
+        <v>225929.8</v>
       </c>
       <c r="G15" s="13">
-        <v>8222.78</v>
+        <v>7990.92</v>
       </c>
       <c r="H15" s="13">
-        <v>1644252.85</v>
+        <v>1603792.83</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3628,7 +3643,7 @@
         <v>156643.97</v>
       </c>
       <c r="C16" s="13">
-        <v>22268.77</v>
+        <v>21787.4</v>
       </c>
       <c r="D16" s="13">
         <v>0</v>
@@ -3637,13 +3652,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="13">
-        <v>178912.74</v>
+        <v>178431.37</v>
       </c>
       <c r="G16" s="13">
-        <v>9591.47</v>
+        <v>9355.46</v>
       </c>
       <c r="H16" s="13">
-        <v>1832757.06</v>
+        <v>1791579.66</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3654,7 +3669,7 @@
         <v>98470.52</v>
       </c>
       <c r="C17" s="13">
-        <v>22268.69</v>
+        <v>21787.31</v>
       </c>
       <c r="D17" s="13">
         <v>0</v>
@@ -3663,13 +3678,13 @@
         <v>0</v>
       </c>
       <c r="F17" s="13">
-        <v>120739.21</v>
+        <v>120257.83</v>
       </c>
       <c r="G17" s="13">
-        <v>10691.08</v>
+        <v>10450.88</v>
       </c>
       <c r="H17" s="13">
-        <v>1964187.35</v>
+        <v>1922288.37</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3680,7 +3695,7 @@
         <v>33586.47</v>
       </c>
       <c r="C18" s="13">
-        <v>22268.75</v>
+        <v>21787.38</v>
       </c>
       <c r="D18" s="13">
         <v>0</v>
@@ -3689,13 +3704,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="13">
-        <v>55855.22</v>
+        <v>55373.85</v>
       </c>
       <c r="G18" s="13">
-        <v>11457.76</v>
+        <v>11213.35</v>
       </c>
       <c r="H18" s="13">
-        <v>2031500.33</v>
+        <v>1988875.57</v>
       </c>
     </row>
   </sheetData>
@@ -3717,7 +3732,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4578,7 +4593,7 @@
         <v>313</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>314</v>
@@ -4589,39 +4604,39 @@
         <v>315</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
+        <v>320</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C51" s="12" t="s">
+      <c r="D51" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F51" s="12" t="s">
         <v>319</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,7 +4653,7 @@
         <v>325</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="F52" s="12" t="s">
         <v>326</v>
@@ -4658,10 +4673,30 @@
         <v>330</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>252</v>
+        <v>183</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>331</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
